--- a/ASP/DR.xlsx
+++ b/ASP/DR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zojamancekpali/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{97740676-3022-2942-BADF-F84A15AB169E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{57173540-4C32-E542-AD15-3309DD6C71C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{9C1E857C-3231-324A-BD9C-890F484D2F6F}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
   <si>
     <t>Condition</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>118/70</t>
+  </si>
+  <si>
+    <t>163/85</t>
+  </si>
+  <si>
+    <t>117/73</t>
   </si>
   <si>
     <t>114/77</t>
@@ -123,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -137,6 +143,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,10 +171,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,13 +524,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -703,7 +716,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13">
         <v>30</v>
@@ -719,6 +732,9 @@
       <c r="B14">
         <v>2</v>
       </c>
+      <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D14">
         <v>0</v>
       </c>
@@ -747,6 +763,9 @@
       <c r="B16">
         <v>2</v>
       </c>
+      <c r="C16" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="D16">
         <v>30</v>
       </c>
@@ -762,7 +781,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -793,7 +812,7 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19">
         <v>30</v>
@@ -810,7 +829,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -841,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>30</v>
@@ -858,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -889,7 +908,7 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25">
         <v>30</v>
@@ -906,7 +925,7 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -937,7 +956,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D28">
         <v>30</v>
